--- a/data/scenarios/feed_dist/limit_imports.xlsx
+++ b/data/scenarios/feed_dist/limit_imports.xlsx
@@ -1,26 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\scenarios\feed_dist\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2CC16C-95F3-4719-9396-19B0527F23B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="FeedMgmt" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="30">
+  <si>
+    <t>f_prod_system</t>
+  </si>
+  <si>
+    <t>f_crop_prod</t>
+  </si>
+  <si>
+    <t>f_by_prod</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>val_is</t>
+  </si>
+  <si>
+    <t>y_0</t>
+  </si>
+  <si>
+    <t>conventional</t>
+  </si>
+  <si>
+    <t>linseed</t>
+  </si>
+  <si>
+    <t>max_total_imported</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>maize</t>
+  </si>
+  <si>
+    <t>soybeans</t>
+  </si>
+  <si>
+    <t>organic</t>
+  </si>
+  <si>
+    <t>fish meal</t>
+  </si>
+  <si>
+    <t>luzern meal</t>
+  </si>
+  <si>
+    <t>maize gluten meal</t>
+  </si>
+  <si>
+    <t>milling by-products from wheat, barley or rye</t>
+  </si>
+  <si>
+    <t>palm kernel expeller</t>
+  </si>
+  <si>
+    <t>rapeseed meal</t>
+  </si>
+  <si>
+    <t>soybean meal</t>
+  </si>
+  <si>
+    <t>soybean protein concentrate</t>
+  </si>
+  <si>
+    <t>sunflower seed meal</t>
+  </si>
+  <si>
+    <t>potatoe protein</t>
+  </si>
+  <si>
+    <t>rapeseed cake</t>
+  </si>
+  <si>
+    <t>sugar beet molasses</t>
+  </si>
+  <si>
+    <t>sugar beet pulp</t>
+  </si>
+  <si>
+    <t>slack</t>
+  </si>
+  <si>
+    <t>Max imports derived from GeoDistributor solution</t>
+  </si>
+  <si>
+    <t>Some slack required to solve with fixed feed rations</t>
+  </si>
+  <si>
+    <t>wheat distillers grain</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +140,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +209,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +500,725 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2">
+        <f>H2*$L$2</f>
+        <v>221.76701078302699</v>
+      </c>
+      <c r="H2" s="3">
+        <v>221.76701078302699</v>
+      </c>
+      <c r="I2" s="8">
+        <v>277.74151881784002</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <f>H3*$L$2</f>
+        <v>10632.753913061701</v>
+      </c>
+      <c r="H3" s="3">
+        <v>10632.753913061701</v>
+      </c>
+      <c r="I3" s="8">
+        <v>15355.0004665626</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2">
+        <f>H4*$L$2</f>
+        <v>5.6530214424543597E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>5.6530214424543597E-2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1477.17105547918</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <f>H5*$L$2</f>
+        <v>0.44167698630594598</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.44167698630594598</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.49337892917456799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
+        <f>H6*$L$2</f>
+        <v>212.23190159495999</v>
+      </c>
+      <c r="H6" s="3">
+        <v>212.23190159495999</v>
+      </c>
+      <c r="I6" s="8">
+        <v>216.59369645596601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <f>H7*$L$2</f>
+        <v>1255.0327074596801</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1255.0327074596801</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1256.3970730158601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F8" s="2"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2">
+        <f>H9*$L$2</f>
+        <v>3368.0419796968599</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3368.0419796968599</v>
+      </c>
+      <c r="I9" s="8">
+        <v>3368.0419796968599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <f>H10*$L$2</f>
+        <v>4562.3495916391103</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4562.3495916391103</v>
+      </c>
+      <c r="I10" s="8">
+        <v>7313.0401321795798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2">
+        <f>H11*$L$2</f>
+        <v>12463.9045818143</v>
+      </c>
+      <c r="H11" s="3">
+        <v>12463.9045818143</v>
+      </c>
+      <c r="I11" s="8">
+        <v>13440.928579851099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2">
+        <f>H12*$L$2</f>
+        <v>17264.640600857601</v>
+      </c>
+      <c r="H12" s="3">
+        <v>17264.640600857601</v>
+      </c>
+      <c r="I12" s="8">
+        <v>23739.411004242898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2">
+        <f>H13*$L$2</f>
+        <v>229.115938658218</v>
+      </c>
+      <c r="H13" s="3">
+        <v>229.115938658218</v>
+      </c>
+      <c r="I13" s="8">
+        <v>9172.4472142937193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <f>H14*$L$2</f>
+        <v>26789.094459022301</v>
+      </c>
+      <c r="H14" s="3">
+        <v>26789.094459022301</v>
+      </c>
+      <c r="I14" s="8">
+        <v>85544.916257249206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2">
+        <f>H15*$L$2</f>
+        <v>186040.00038967701</v>
+      </c>
+      <c r="H15" s="3">
+        <v>186040.00038967701</v>
+      </c>
+      <c r="I15" s="8">
+        <v>199455.791267783</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2">
+        <f>H16*$L$2</f>
+        <v>2287.2046233297801</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2287.2046233297801</v>
+      </c>
+      <c r="I16" s="8">
+        <v>2287.2046233297801</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2">
+        <f>H17*$L$2</f>
+        <v>4643.8855584189996</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4643.8855584189996</v>
+      </c>
+      <c r="I17" s="8">
+        <v>6020.2232845055596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
+        <f>H18*$L$2</f>
+        <v>115.478986635086</v>
+      </c>
+      <c r="H18" s="3">
+        <v>115.478986635086</v>
+      </c>
+      <c r="I18" s="8">
+        <v>115.478986635086</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2">
+        <f>H19*$L$2</f>
+        <v>19.831925878161702</v>
+      </c>
+      <c r="H19" s="3">
+        <v>19.831925878161702</v>
+      </c>
+      <c r="I19" s="8">
+        <v>22.372654687641699</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2">
+        <f>H20*$L$2</f>
+        <v>479.03642805588498</v>
+      </c>
+      <c r="H20" s="3">
+        <v>479.03642805588498</v>
+      </c>
+      <c r="I20" s="8">
+        <v>479.93887527151298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
+        <f>H21*$L$2</f>
+        <v>22.128789029251902</v>
+      </c>
+      <c r="H21" s="3">
+        <v>22.128789029251902</v>
+      </c>
+      <c r="I21" s="8">
+        <v>26.6141997260011</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
+        <f>H22*$L$2</f>
+        <v>2.5449007306199798</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2.5449007306199798</v>
+      </c>
+      <c r="I22" s="8">
+        <v>10.805582581173001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
+        <f>H23*$L$2</f>
+        <v>3650.8302595843102</v>
+      </c>
+      <c r="H23" s="3">
+        <v>3650.8302595843102</v>
+      </c>
+      <c r="I23" s="8">
+        <v>3650.9173723816698</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2">
+        <f>H24*$L$2</f>
+        <v>2570.6415719882698</v>
+      </c>
+      <c r="H24" s="3">
+        <v>2570.6415719882698</v>
+      </c>
+      <c r="I24" s="8">
+        <v>14044.5428640952</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2">
+        <f>H25*$L$2</f>
+        <v>2749.82350179178</v>
+      </c>
+      <c r="H25" s="3">
+        <v>2749.82350179178</v>
+      </c>
+      <c r="I25" s="8">
+        <v>2762.2152579284998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2">
+        <f>H26*$L$2</f>
+        <v>1.44775753125088E-2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1.44775753125088E-2</v>
+      </c>
+      <c r="I26" s="8">
+        <v>1.44775753125088E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="2">
+        <f>H27*$L$2</f>
+        <v>17.6212891853509</v>
+      </c>
+      <c r="H27" s="3">
+        <v>17.6212891853509</v>
+      </c>
+      <c r="I27" s="8">
+        <v>29.629215679966801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="2">
+        <f>H28*$L$2</f>
+        <v>45.181469283322002</v>
+      </c>
+      <c r="H28" s="3">
+        <v>45.181469283322002</v>
+      </c>
+      <c r="I28" s="8">
+        <v>64.527870096764701</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="2">
+        <f>H29*$L$2</f>
+        <v>28.468727720316899</v>
+      </c>
+      <c r="H29" s="3">
+        <v>28.468727720316899</v>
+      </c>
+      <c r="I29" s="8">
+        <v>29.7400088261716</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="2">
+        <f>H30*$L$2</f>
+        <v>10.2799105164395</v>
+      </c>
+      <c r="H30" s="3">
+        <v>10.2799105164395</v>
+      </c>
+      <c r="I30" s="8">
+        <v>37.059473988472597</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>